--- a/data/Sistema_de_Notificacion_de_Muertes_Violentas/svmvIncidentes.xlsx
+++ b/data/Sistema_de_Notificacion_de_Muertes_Violentas/svmvIncidentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Sistema_de_Notificacion_de_Muertes_Violentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D031EC3-3CC6-4C2E-9C37-B6A53E69B2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E007CF11-D9AC-4F14-879E-8917B4AE0EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9CFC54A2-FB65-C045-ACC9-D5EBAFBDCE35}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Tipo de Incidente</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Total de víctimas mujeres </t>
+  </si>
+  <si>
+    <t>Manera pendiente</t>
   </si>
 </sst>
 </file>
@@ -432,13 +435,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1B44BE-364E-EC48-9E9B-83F94D0251FB}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,11 +469,17 @@
       <c r="I1" s="1">
         <v>2024</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -484,7 +493,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1">
         <v>29</v>
@@ -499,11 +508,17 @@
         <v>41</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" ref="J2:J10" si="0">SUM(B2:I2)</f>
-        <v>307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1">
+        <f t="shared" ref="L2:L9" si="0">SUM(B2:K2)</f>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -517,7 +532,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1">
         <v>28</v>
@@ -529,14 +544,20 @@
         <v>28</v>
       </c>
       <c r="I3" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J3" s="1">
+        <v>41</v>
+      </c>
+      <c r="K3" s="1">
+        <v>4</v>
+      </c>
+      <c r="L3" s="1">
         <f t="shared" si="0"/>
-        <v>222</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -565,11 +586,17 @@
         <v>15</v>
       </c>
       <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -598,11 +625,17 @@
         <v>6</v>
       </c>
       <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -631,11 +664,17 @@
         <v>6</v>
       </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -649,7 +688,7 @@
         <v>5</v>
       </c>
       <c r="E7" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -664,11 +703,17 @@
         <v>0</v>
       </c>
       <c r="J7" s="1">
+        <v>4</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -694,85 +739,134 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>13</v>
+      </c>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <f>SUM(B9:K9)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>89</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C10" s="1">
         <v>97</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D10" s="1">
+        <v>95</v>
+      </c>
+      <c r="E10" s="1">
+        <v>83</v>
+      </c>
+      <c r="F10" s="2">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2">
+        <v>84</v>
+      </c>
+      <c r="H10" s="2">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2">
+        <v>96</v>
+      </c>
+      <c r="J10" s="2">
+        <v>91</v>
+      </c>
+      <c r="K10" s="2">
+        <v>15</v>
+      </c>
+      <c r="L10" s="1">
+        <f>SUM(B10:K10)</f>
+        <v>809</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>90</v>
+      </c>
+      <c r="C11" s="1">
+        <v>97</v>
+      </c>
+      <c r="D11" s="1">
+        <v>97</v>
+      </c>
+      <c r="E11" s="1">
+        <v>86</v>
+      </c>
+      <c r="F11" s="1">
+        <v>69</v>
+      </c>
+      <c r="G11" s="1">
+        <v>84</v>
+      </c>
+      <c r="H11" s="1">
         <v>92</v>
       </c>
-      <c r="E9" s="1">
-        <v>81</v>
-      </c>
-      <c r="F9" s="2">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2">
-        <v>84</v>
-      </c>
-      <c r="H9" s="2">
-        <v>89</v>
-      </c>
-      <c r="I9" s="2">
-        <v>95</v>
-      </c>
-      <c r="J9" s="1">
-        <f t="shared" si="0"/>
-        <v>696</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <f>SUM(B2:B8)</f>
-        <v>90</v>
-      </c>
-      <c r="C10" s="1">
-        <f>SUM(C2:C8)</f>
-        <v>97</v>
-      </c>
-      <c r="D10" s="1">
-        <f>SUM(D2:D8)</f>
-        <v>97</v>
-      </c>
-      <c r="E10" s="1">
-        <f t="shared" ref="D10:I10" si="1">SUM(E2:E8)</f>
-        <v>84</v>
-      </c>
-      <c r="F10" s="1">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-      <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>92</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="1"/>
+      <c r="I11" s="1">
         <v>100</v>
       </c>
-      <c r="J10" s="1">
-        <f t="shared" si="0"/>
-        <v>713</v>
+      <c r="J11" s="1">
+        <v>91</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="1">
+        <f>SUM(B11:K11)</f>
+        <v>821</v>
       </c>
     </row>
   </sheetData>

--- a/data/Sistema_de_Notificacion_de_Muertes_Violentas/svmvIncidentes.xlsx
+++ b/data/Sistema_de_Notificacion_de_Muertes_Violentas/svmvIncidentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Sistema_de_Notificacion_de_Muertes_Violentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E007CF11-D9AC-4F14-879E-8917B4AE0EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9664275B-DA21-400F-A954-CC1141F75C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9CFC54A2-FB65-C045-ACC9-D5EBAFBDCE35}"/>
   </bookViews>
@@ -511,11 +511,11 @@
         <v>33</v>
       </c>
       <c r="K2" s="1">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="L2" s="1">
-        <f t="shared" ref="L2:L9" si="0">SUM(B2:K2)</f>
-        <v>351</v>
+        <f t="shared" ref="L2:L8" si="0">SUM(B2:K2)</f>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -550,11 +550,11 @@
         <v>41</v>
       </c>
       <c r="K3" s="1">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="L3" s="1">
         <f t="shared" si="0"/>
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -784,11 +784,11 @@
         <v>13</v>
       </c>
       <c r="K9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" s="1">
         <f>SUM(B9:K9)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -820,14 +820,14 @@
         <v>96</v>
       </c>
       <c r="J10" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K10" s="2">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L10" s="1">
         <f>SUM(B10:K10)</f>
-        <v>809</v>
+        <v>834</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -859,14 +859,14 @@
         <v>100</v>
       </c>
       <c r="J11" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K11" s="1">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L11" s="1">
         <f>SUM(B11:K11)</f>
-        <v>821</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
